--- a/genotoscope_data/misc/hl_relevant_transcripts.xlsx
+++ b/genotoscope_data/misc/hl_relevant_transcripts.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="557">
   <si>
     <t xml:space="preserve">Gene</t>
   </si>
   <si>
-    <t xml:space="preserve">ensembl GRCh37.p13</t>
+    <t xml:space="preserve">ensembl GRCh38.p14</t>
   </si>
   <si>
     <t xml:space="preserve">clinical_exons</t>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">ATP6V1B1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000234396.4</t>
+    <t xml:space="preserve">ENST00000234396.10</t>
   </si>
   <si>
     <t xml:space="preserve">2-14</t>
@@ -52,16 +52,19 @@
     <t xml:space="preserve">ALMS1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000264448.6</t>
+    <t xml:space="preserve">ENST00000613296.6 </t>
   </si>
   <si>
     <t xml:space="preserve">1-23</t>
   </si>
   <si>
+    <t xml:space="preserve">mane_transcript</t>
+  </si>
+  <si>
     <t xml:space="preserve">BSND</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000371265.4</t>
+    <t xml:space="preserve">ENST00000651561.1</t>
   </si>
   <si>
     <t xml:space="preserve">1-4</t>
@@ -70,7 +73,7 @@
     <t xml:space="preserve">CEACAM16</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000587331.1</t>
+    <t xml:space="preserve">ENST00000587331.7</t>
   </si>
   <si>
     <t xml:space="preserve">2-7</t>
@@ -79,7 +82,7 @@
     <t xml:space="preserve">CISD2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000273986.4</t>
+    <t xml:space="preserve">ENST00000273986.10</t>
   </si>
   <si>
     <t xml:space="preserve">1-3</t>
@@ -88,7 +91,7 @@
     <t xml:space="preserve">CLPP</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000245816.4</t>
+    <t xml:space="preserve">ENST00000245816.11</t>
   </si>
   <si>
     <t xml:space="preserve">1-6</t>
@@ -97,7 +100,7 @@
     <t xml:space="preserve">COL4A3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000396578.3</t>
+    <t xml:space="preserve">ENST00000396578.8</t>
   </si>
   <si>
     <t xml:space="preserve">1-52</t>
@@ -106,7 +109,7 @@
     <t xml:space="preserve">COL4A4</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000396625.3</t>
+    <t xml:space="preserve">ENST00000396625.5</t>
   </si>
   <si>
     <t xml:space="preserve">2-48</t>
@@ -115,7 +118,7 @@
     <t xml:space="preserve">EPS8</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000281172.5</t>
+    <t xml:space="preserve">ENST00000281172.10</t>
   </si>
   <si>
     <t xml:space="preserve">2-21</t>
@@ -124,7 +127,7 @@
     <t xml:space="preserve">ESPN</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000377828.1</t>
+    <t xml:space="preserve">ENST00000645284.1</t>
   </si>
   <si>
     <t xml:space="preserve">1-13</t>
@@ -133,22 +136,25 @@
     <t xml:space="preserve">ESRRB</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000509242.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-11</t>
+    <t xml:space="preserve">ENST00000644823.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not_canonical,adjust_exons_to_coding</t>
   </si>
   <si>
     <t xml:space="preserve">GIPC3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000322315.5</t>
+    <t xml:space="preserve">ENST00000644452.3</t>
   </si>
   <si>
     <t xml:space="preserve">GJB2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000382848.4</t>
+    <t xml:space="preserve">ENST00000382848.5</t>
   </si>
   <si>
     <t xml:space="preserve">1-2</t>
@@ -157,7 +163,7 @@
     <t xml:space="preserve">GPR98 (ADGRV1)</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000405460.2</t>
+    <t xml:space="preserve">ENST00000405460.9</t>
   </si>
   <si>
     <t xml:space="preserve">1-90</t>
@@ -166,7 +172,7 @@
     <t xml:space="preserve">GRHL2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000251808.3</t>
+    <t xml:space="preserve">ENST00000646743.1</t>
   </si>
   <si>
     <t xml:space="preserve">1-16</t>
@@ -175,13 +181,13 @@
     <t xml:space="preserve">GRXCR1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000399770.2</t>
+    <t xml:space="preserve">ENST00000399770.3</t>
   </si>
   <si>
     <t xml:space="preserve">LARS2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000265537.3</t>
+    <t xml:space="preserve">ENST00000645846.2</t>
   </si>
   <si>
     <t xml:space="preserve">3-22</t>
@@ -190,13 +196,13 @@
     <t xml:space="preserve">LHFPL5</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000360215.1</t>
+    <t xml:space="preserve">ENST00000360215.3</t>
   </si>
   <si>
     <t xml:space="preserve">MYH9</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000216181.5</t>
+    <t xml:space="preserve">ENST00000216181.11</t>
   </si>
   <si>
     <t xml:space="preserve">2-41</t>
@@ -205,7 +211,7 @@
     <t xml:space="preserve">MYO3A</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000265944.5</t>
+    <t xml:space="preserve">ENST00000642920.2</t>
   </si>
   <si>
     <t xml:space="preserve">3-35</t>
@@ -214,7 +220,7 @@
     <t xml:space="preserve">MYO15A</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000205890.5</t>
+    <t xml:space="preserve">ENST00000647165.2</t>
   </si>
   <si>
     <t xml:space="preserve">2-66</t>
@@ -223,7 +229,7 @@
     <t xml:space="preserve">OTOGL</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000458043.2</t>
+    <t xml:space="preserve">ENST00000547103.7</t>
   </si>
   <si>
     <t xml:space="preserve">1-58</t>
@@ -232,7 +238,7 @@
     <t xml:space="preserve">POU3F4</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000373200.2</t>
+    <t xml:space="preserve">ENST00000644024.2</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -241,13 +247,13 @@
     <t xml:space="preserve">POU4F3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000361360.2</t>
+    <t xml:space="preserve">ENST00000646991.2</t>
   </si>
   <si>
     <t xml:space="preserve">PTPRQ</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000551573.1</t>
+    <t xml:space="preserve">ENST00000644991.3</t>
   </si>
   <si>
     <t xml:space="preserve">1-45</t>
@@ -256,7 +262,7 @@
     <t xml:space="preserve">S1PR2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000590320.1</t>
+    <t xml:space="preserve">ENST00000646641.1</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
@@ -265,13 +271,13 @@
     <t xml:space="preserve">SIX1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000247182.6</t>
+    <t xml:space="preserve">ENST00000645694.3</t>
   </si>
   <si>
     <t xml:space="preserve">SLC26A4</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000265715.3</t>
+    <t xml:space="preserve">ENST00000644269.2</t>
   </si>
   <si>
     <t xml:space="preserve">1-21</t>
@@ -280,7 +286,7 @@
     <t xml:space="preserve">SLC52A3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000217254.7</t>
+    <t xml:space="preserve">ENST00000645534.1</t>
   </si>
   <si>
     <t xml:space="preserve">2-5</t>
@@ -289,13 +295,13 @@
     <t xml:space="preserve">SLITRK6</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000400286.2</t>
+    <t xml:space="preserve">ENST00000647374.2</t>
   </si>
   <si>
     <t xml:space="preserve">SMPX</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000379494.3</t>
+    <t xml:space="preserve">ENST00000379494.4</t>
   </si>
   <si>
     <t xml:space="preserve">2-4</t>
@@ -304,19 +310,19 @@
     <t xml:space="preserve">SNAI2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000020945.1</t>
+    <t xml:space="preserve">ENST00000020945.4</t>
   </si>
   <si>
     <t xml:space="preserve">SOX10</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000396884.2</t>
+    <t xml:space="preserve">ENST00000396884.8</t>
   </si>
   <si>
     <t xml:space="preserve">STRC</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000450892.2</t>
+    <t xml:space="preserve">ENST00000450892.7</t>
   </si>
   <si>
     <t xml:space="preserve">1-29</t>
@@ -325,13 +331,13 @@
     <t xml:space="preserve">TECTA</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000264037.2</t>
+    <t xml:space="preserve">ENST00000264037.6</t>
   </si>
   <si>
     <t xml:space="preserve">TMC1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000297784.5</t>
+    <t xml:space="preserve">ENST00000297784.10</t>
   </si>
   <si>
     <t xml:space="preserve">5-24</t>
@@ -340,19 +346,19 @@
     <t xml:space="preserve">TMIE</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000326431.3</t>
+    <t xml:space="preserve">ENST00000643606.3</t>
   </si>
   <si>
     <t xml:space="preserve">TPRN</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000409012.4</t>
+    <t xml:space="preserve">ENST00000409012.6</t>
   </si>
   <si>
     <t xml:space="preserve">ACTG1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000573283.1</t>
+    <t xml:space="preserve">ENST00000573283.7</t>
   </si>
   <si>
     <t xml:space="preserve">2-6</t>
@@ -361,7 +367,7 @@
     <t xml:space="preserve">BCS1L</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000392109.1</t>
+    <t xml:space="preserve">ENST00000392109.5</t>
   </si>
   <si>
     <t xml:space="preserve">3-9</t>
@@ -376,7 +382,7 @@
     <t xml:space="preserve">CCDC50</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000392456.3</t>
+    <t xml:space="preserve">ENST00000392455.9 </t>
   </si>
   <si>
     <t xml:space="preserve">1-5, 7-12</t>
@@ -385,7 +391,7 @@
     <t xml:space="preserve">CEP78</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000376597.4</t>
+    <t xml:space="preserve">ENST00000376597.9</t>
   </si>
   <si>
     <t xml:space="preserve">3-15</t>
@@ -394,7 +400,7 @@
     <t xml:space="preserve">CHD7</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000423902.2</t>
+    <t xml:space="preserve">ENST00000423902.7</t>
   </si>
   <si>
     <t xml:space="preserve">2-38</t>
@@ -403,7 +409,7 @@
     <t xml:space="preserve">COCH</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000216361.4</t>
+    <t xml:space="preserve">ENST00000216361.9</t>
   </si>
   <si>
     <t xml:space="preserve">1-11</t>
@@ -412,7 +418,7 @@
     <t xml:space="preserve">COL11A2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000341947.2</t>
+    <t xml:space="preserve">ENST00000341947.7</t>
   </si>
   <si>
     <t xml:space="preserve">1-66</t>
@@ -421,7 +427,7 @@
     <t xml:space="preserve">COL4A5</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000328300.6</t>
+    <t xml:space="preserve">ENST00000328300.11</t>
   </si>
   <si>
     <t xml:space="preserve">1-53</t>
@@ -430,7 +436,7 @@
     <t xml:space="preserve">DFNA5</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000342947.3</t>
+    <t xml:space="preserve">ENST00000342947.9</t>
   </si>
   <si>
     <t xml:space="preserve">3-10</t>
@@ -439,19 +445,22 @@
     <t xml:space="preserve">DFNB59 (PJVK)</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000409117.3</t>
+    <t xml:space="preserve">ENST00000644580.2</t>
   </si>
   <si>
     <t xml:space="preserve">DIABLO</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000443649.3</t>
+    <t xml:space="preserve">ENST00000443649.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transcript_id_retired</t>
   </si>
   <si>
     <t xml:space="preserve">EDN3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000337938.2</t>
+    <t xml:space="preserve">ENST00000337938.7</t>
   </si>
   <si>
     <t xml:space="preserve">1-5</t>
@@ -460,7 +469,7 @@
     <t xml:space="preserve">GJB6</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000356192.6</t>
+    <t xml:space="preserve">ENST00000647029.1</t>
   </si>
   <si>
     <t xml:space="preserve">5</t>
@@ -469,7 +478,7 @@
     <t xml:space="preserve">GPSM2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000264126.3</t>
+    <t xml:space="preserve">ENST00000264126.9</t>
   </si>
   <si>
     <t xml:space="preserve">2-15</t>
@@ -478,19 +487,19 @@
     <t xml:space="preserve">HARS</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000504156.1</t>
+    <t xml:space="preserve">ENST00000504156.7</t>
   </si>
   <si>
     <t xml:space="preserve">HARS2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000230771.3</t>
+    <t xml:space="preserve">ENST00000230771.9</t>
   </si>
   <si>
     <t xml:space="preserve">ILDR1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000344209.5</t>
+    <t xml:space="preserve">ENST00000344209.10</t>
   </si>
   <si>
     <t xml:space="preserve">1-5, 7-8</t>
@@ -499,7 +508,7 @@
     <t xml:space="preserve">KARS</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000319410.5</t>
+    <t xml:space="preserve">ENST00000319410.9</t>
   </si>
   <si>
     <t xml:space="preserve">3-14</t>
@@ -508,7 +517,7 @@
     <t xml:space="preserve">KCNE1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000399286.2</t>
+    <t xml:space="preserve">ENST00000399286.3</t>
   </si>
   <si>
     <t xml:space="preserve">4</t>
@@ -517,7 +526,7 @@
     <t xml:space="preserve">KCNQ4</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000347132.5</t>
+    <t xml:space="preserve">ENST00000347132.10</t>
   </si>
   <si>
     <t xml:space="preserve">1-8, 10-14</t>
@@ -526,7 +535,7 @@
     <t xml:space="preserve">KITLG</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000228280.5</t>
+    <t xml:space="preserve">ENST00000644744.1</t>
   </si>
   <si>
     <t xml:space="preserve">1-5, 7-9</t>
@@ -535,7 +544,7 @@
     <t xml:space="preserve">MARVELD2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000325631.5</t>
+    <t xml:space="preserve">ENST00000325631.10</t>
   </si>
   <si>
     <t xml:space="preserve">2,4-7</t>
@@ -544,7 +553,7 @@
     <t xml:space="preserve">MYH14</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000601313.1</t>
+    <t xml:space="preserve">ENST00000642316.2</t>
   </si>
   <si>
     <t xml:space="preserve">2-16, 18-43</t>
@@ -553,7 +562,7 @@
     <t xml:space="preserve">MYO6</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000369977.3</t>
+    <t xml:space="preserve">ENST00000369985.9</t>
   </si>
   <si>
     <t xml:space="preserve">2-33</t>
@@ -562,7 +571,7 @@
     <t xml:space="preserve">NLRP3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000336119.3</t>
+    <t xml:space="preserve">ENST00000336119.8</t>
   </si>
   <si>
     <t xml:space="preserve">1-3, 5, 7-10</t>
@@ -571,7 +580,7 @@
     <t xml:space="preserve">PRPS1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000372435.4</t>
+    <t xml:space="preserve">ENST00000372435.10</t>
   </si>
   <si>
     <t xml:space="preserve">1-7</t>
@@ -580,13 +589,13 @@
     <t xml:space="preserve">SLC52A2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000329994.2</t>
+    <t xml:space="preserve">ENST00000329994.7</t>
   </si>
   <si>
     <t xml:space="preserve">SYNE4</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000324444.3</t>
+    <t xml:space="preserve">ENST00000324444.9</t>
   </si>
   <si>
     <t xml:space="preserve">1,2,4-8</t>
@@ -595,13 +604,13 @@
     <t xml:space="preserve">TBC1D24</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000567020.1</t>
+    <t xml:space="preserve">ENST00000567020.7</t>
   </si>
   <si>
     <t xml:space="preserve">USH1G</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000319642.1</t>
+    <t xml:space="preserve">ENST00000614341.5</t>
   </si>
   <si>
     <t xml:space="preserve">2-3</t>
@@ -610,7 +619,7 @@
     <t xml:space="preserve">USH2A</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000307340.3</t>
+    <t xml:space="preserve">ENST00000307340.8</t>
   </si>
   <si>
     <t xml:space="preserve">2-72</t>
@@ -622,22 +631,19 @@
     <t xml:space="preserve">WFS1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000226760.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-8</t>
+    <t xml:space="preserve">ENST00000226760.5</t>
   </si>
   <si>
     <t xml:space="preserve">ADCY1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000297323.7</t>
+    <t xml:space="preserve">ENST00000297323.12</t>
   </si>
   <si>
     <t xml:space="preserve">1-20</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000432715.1</t>
+    <t xml:space="preserve">ENST00000432715.5</t>
   </si>
   <si>
     <t xml:space="preserve">-(1,10)</t>
@@ -646,13 +652,13 @@
     <t xml:space="preserve">CABP2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000294288.4</t>
+    <t xml:space="preserve">ENST00000294288.5</t>
   </si>
   <si>
     <t xml:space="preserve">1-5,7</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000545205.1</t>
+    <t xml:space="preserve">ENST00000545205.2</t>
   </si>
   <si>
     <t xml:space="preserve">-(1,2)</t>
@@ -664,19 +670,19 @@
     <t xml:space="preserve">CACNA1D</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000288139.4</t>
+    <t xml:space="preserve">ENST00000288139.11</t>
   </si>
   <si>
     <t xml:space="preserve">1-49</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000422281.2</t>
+    <t xml:space="preserve">ENST00000422281.7</t>
   </si>
   <si>
     <t xml:space="preserve">-8</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000350061.5</t>
+    <t xml:space="preserve">ENST00000350061.11</t>
   </si>
   <si>
     <t xml:space="preserve">no_distinct_coding_exons</t>
@@ -685,19 +691,19 @@
     <t xml:space="preserve">CDC14A</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000361544.6</t>
+    <t xml:space="preserve">ENST00000361544.11</t>
   </si>
   <si>
     <t xml:space="preserve">1-15</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000336454.3</t>
+    <t xml:space="preserve">ENST00000336454.5</t>
   </si>
   <si>
     <t xml:space="preserve">-16</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000370124.3</t>
+    <t xml:space="preserve">ENST00000370124.8</t>
   </si>
   <si>
     <t xml:space="preserve">-11</t>
@@ -706,40 +712,40 @@
     <t xml:space="preserve">ENST00000544534.1</t>
   </si>
   <si>
+    <t xml:space="preserve">transcript_id_not_found, matched_by_protein_length</t>
+  </si>
+  <si>
     <t xml:space="preserve">ENST00000542213.1</t>
   </si>
   <si>
     <t xml:space="preserve">ENST00000644844.1</t>
   </si>
   <si>
-    <t xml:space="preserve">only_grch38</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDH23</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000224721.6</t>
+    <t xml:space="preserve">ENST00000224721.12</t>
   </si>
   <si>
     <t xml:space="preserve">2-70</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000398788.3</t>
+    <t xml:space="preserve">ENST00000398788.4</t>
   </si>
   <si>
     <t xml:space="preserve">-1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000461841.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000398809.4</t>
+    <t xml:space="preserve">ENST00000461841.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000398809.9</t>
   </si>
   <si>
     <t xml:space="preserve">-14</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000299366.7</t>
+    <t xml:space="preserve">ENST00000299366.11</t>
   </si>
   <si>
     <t xml:space="preserve">-26</t>
@@ -754,34 +760,37 @@
     <t xml:space="preserve">CD164</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000310786.4</t>
+    <t xml:space="preserve">ENST00000310786.10</t>
   </si>
   <si>
     <t xml:space="preserve">ENST00000275080.7</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000324953.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000413644.2</t>
+    <t xml:space="preserve">transcript_id_not_found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000324953.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000413644.6</t>
   </si>
   <si>
     <t xml:space="preserve">-6</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000504373.1</t>
+    <t xml:space="preserve">ENST00000504373.2</t>
   </si>
   <si>
     <t xml:space="preserve">CIB2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000258930.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000539011.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000557846.1</t>
+    <t xml:space="preserve">ENST00000258930.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000539011.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000557846.5</t>
   </si>
   <si>
     <t xml:space="preserve">-3</t>
@@ -790,37 +799,37 @@
     <t xml:space="preserve">CLIC5</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000185206.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000339561.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000544153.1</t>
+    <t xml:space="preserve">ENST00000185206.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000339561.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000544153.3</t>
   </si>
   <si>
     <t xml:space="preserve">CLDN14</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000399137.1</t>
+    <t xml:space="preserve">ENST00000399137.5</t>
   </si>
   <si>
     <t xml:space="preserve">CLRN1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000327047.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000295911.2</t>
+    <t xml:space="preserve">ENST00000327047.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000295911.6</t>
   </si>
   <si>
     <t xml:space="preserve">-(1,4)</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000328863.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000468836.1</t>
+    <t xml:space="preserve">ENST00000328863.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000468836.2</t>
   </si>
   <si>
     <t xml:space="preserve">-(2,3)</t>
@@ -829,28 +838,28 @@
     <t xml:space="preserve">DFNB31 (WHRN)</t>
   </si>
   <si>
+    <t xml:space="preserve">ENST00000362057.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000265134.10</t>
+  </si>
+  <si>
     <t xml:space="preserve">ENST00000362057.3</t>
   </si>
   <si>
-    <t xml:space="preserve">1-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000265134.6</t>
-  </si>
-  <si>
     <t xml:space="preserve">DIAPH1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000448451.1</t>
+    <t xml:space="preserve">ENST00000389054.8</t>
   </si>
   <si>
     <t xml:space="preserve">1-28</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000389057.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000647433.1</t>
+    <t xml:space="preserve">ENST00000518047.5</t>
   </si>
   <si>
     <t xml:space="preserve">-(28,29)</t>
@@ -859,13 +868,13 @@
     <t xml:space="preserve">EDNRB</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000334286.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000377211.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000446573.1</t>
+    <t xml:space="preserve">ENST00000646948.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000643890.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000646607.2</t>
   </si>
   <si>
     <t xml:space="preserve">-7</t>
@@ -874,61 +883,52 @@
     <t xml:space="preserve">EYA1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000340726.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000388742.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000388740.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000493349.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000465115.1</t>
+    <t xml:space="preserve">ENST00000340726.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000388742.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000388740.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000303824.11</t>
   </si>
   <si>
     <t xml:space="preserve">EYA4</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000367895.5</t>
+    <t xml:space="preserve">ENST00000355286.12</t>
   </si>
   <si>
     <t xml:space="preserve">2-20</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000355167.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">-19</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000355286.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000452339.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000531901.1</t>
+    <t xml:space="preserve">ENST00000452339.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000531901.5</t>
   </si>
   <si>
     <t xml:space="preserve">HGF</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000222390.5</t>
+    <t xml:space="preserve">ENST00000222390.11</t>
   </si>
   <si>
     <t xml:space="preserve">1-18</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000444829.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000457544.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000423064.2</t>
+    <t xml:space="preserve">ENST00000444829.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000457544.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000423064.7</t>
   </si>
   <si>
     <t xml:space="preserve">-5</t>
@@ -943,79 +943,79 @@
     <t xml:space="preserve">1-25</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000256216.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000515320.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000513628.1</t>
+    <t xml:space="preserve">ENST00000510025.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000515320.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000513628.5</t>
   </si>
   <si>
     <t xml:space="preserve">KCNQ1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000155840.5</t>
+    <t xml:space="preserve">ENST00000155840.12</t>
   </si>
   <si>
     <t xml:space="preserve">LOXHD1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000536736.1</t>
+    <t xml:space="preserve">ENST00000536736.5</t>
   </si>
   <si>
     <t xml:space="preserve">1-30,32-40</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000398686.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000300591.6</t>
+    <t xml:space="preserve">ENST00000398686.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000300591.11</t>
   </si>
   <si>
     <t xml:space="preserve">-(15,24)</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000398705.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000579038.1</t>
+    <t xml:space="preserve">ENST00000398705.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000579038.6</t>
   </si>
   <si>
     <t xml:space="preserve">-(1-3)</t>
   </si>
   <si>
+    <t xml:space="preserve">LRRC51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000289488.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000423494.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-(2,6)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LRTOMT</t>
   </si>
   <si>
+    <t xml:space="preserve">ENST00000307198.11</t>
+  </si>
+  <si>
     <t xml:space="preserve">ENST00000435085.1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000289488.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000423494.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-(2,6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000419228.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">5-9</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000447974.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000307198.7 </t>
+    <t xml:space="preserve">ENST00000541614.5</t>
   </si>
   <si>
     <t xml:space="preserve">MITF</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000394351.3</t>
+    <t xml:space="preserve">ENST00000394351.9</t>
   </si>
   <si>
     <t xml:space="preserve">1-9</t>
@@ -1024,55 +1024,55 @@
     <t xml:space="preserve">ENST00000328528.6</t>
   </si>
   <si>
+    <t xml:space="preserve">ENST00000314557.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000352241.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-(1-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000472437.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">ENST00000314557.6</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000352241.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-(1-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000394355.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000472437.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000394348.1</t>
+    <t xml:space="preserve">ENST00000394348.2</t>
   </si>
   <si>
     <t xml:space="preserve">MSRB3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000355192.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000308259.5</t>
+    <t xml:space="preserve">ENST00000355192.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000308259.10</t>
   </si>
   <si>
     <t xml:space="preserve">3-8</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000535239.1</t>
+    <t xml:space="preserve">ENST00000614640.4</t>
   </si>
   <si>
     <t xml:space="preserve">MYO7A</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000409709.3</t>
+    <t xml:space="preserve">ENST00000409709.9</t>
   </si>
   <si>
     <t xml:space="preserve">1-48</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000409893.1 </t>
+    <t xml:space="preserve">ENST00000409893.6</t>
   </si>
   <si>
     <t xml:space="preserve">27</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000458637.2</t>
+    <t xml:space="preserve">ENST00000458637.6</t>
   </si>
   <si>
     <t xml:space="preserve">OSBPL2</t>
@@ -1093,7 +1093,7 @@
     <t xml:space="preserve">OTOA</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000388958.3</t>
+    <t xml:space="preserve">ENST00000646100.2</t>
   </si>
   <si>
     <t xml:space="preserve">ENST00000388956.4</t>
@@ -1105,40 +1105,40 @@
     <t xml:space="preserve">OTOF</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000403946.3</t>
+    <t xml:space="preserve">ENST00000403946.7</t>
   </si>
   <si>
     <t xml:space="preserve">-(20,32)</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000272371.2</t>
+    <t xml:space="preserve">ENST00000272371.7</t>
   </si>
   <si>
     <t xml:space="preserve">-46</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000338581.6</t>
+    <t xml:space="preserve">ENST00000338581.10</t>
   </si>
   <si>
     <t xml:space="preserve">all</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000402415.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000339598.3</t>
+    <t xml:space="preserve">ENST00000402415.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000339598.8</t>
   </si>
   <si>
     <t xml:space="preserve">OTOG</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000399391.2</t>
+    <t xml:space="preserve">ENST00000399391.7</t>
   </si>
   <si>
     <t xml:space="preserve">1-55</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000399397.1</t>
+    <t xml:space="preserve">ENST00000399397.6</t>
   </si>
   <si>
     <t xml:space="preserve">-2</t>
@@ -1147,76 +1147,85 @@
     <t xml:space="preserve">PAX3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000392069.2</t>
+    <t xml:space="preserve">ENST00000392069.6</t>
   </si>
   <si>
     <t xml:space="preserve">-9</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000409551.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000350526.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000344493.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000409828.3</t>
+    <t xml:space="preserve">ENST00000392070.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000409551.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000350526.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000336840.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000344493.9</t>
   </si>
   <si>
     <t xml:space="preserve">-(3-4)</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000258387.5</t>
+    <t xml:space="preserve">ENST00000258387.6</t>
   </si>
   <si>
     <t xml:space="preserve">PCDH15</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000361849.3</t>
+    <t xml:space="preserve">ENST00000373957.7</t>
   </si>
   <si>
     <t xml:space="preserve">-(1,3,33,35)</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000395430.1</t>
+    <t xml:space="preserve">ENST00000437009.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000395430.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000361849.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000613657.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-(35,36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000621708.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000373965.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000395433.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000320301.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000616114.4</t>
   </si>
   <si>
     <t xml:space="preserve">ENST00000395445.1</t>
   </si>
   <si>
-    <t xml:space="preserve">-(35,36)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000373965.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000395433.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000320301.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000395432.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000644397.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000616114.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000373955.1</t>
+    <t xml:space="preserve">ENST00000373955.5</t>
   </si>
   <si>
     <t xml:space="preserve">-21</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000395438.1</t>
+    <t xml:space="preserve">ENST00000617271.4</t>
   </si>
   <si>
     <t xml:space="preserve">-36</t>
@@ -1231,7 +1240,7 @@
     <t xml:space="preserve">2-17</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000370215.3</t>
+    <t xml:space="preserve">ENST00000370215.7</t>
   </si>
   <si>
     <t xml:space="preserve">-(9,10)</t>
@@ -1243,97 +1252,109 @@
     <t xml:space="preserve">P2RX2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000389110.3</t>
+    <t xml:space="preserve">ENST00000343948.8</t>
   </si>
   <si>
     <t xml:space="preserve">1-10</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000449132.2</t>
+    <t xml:space="preserve">ENST00000449132.6</t>
   </si>
   <si>
     <t xml:space="preserve">-(4-6)</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000343948.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000352418.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000350048.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000351222.4</t>
+    <t xml:space="preserve">ENST00000352418.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000350048.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000643471.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000351222.8</t>
   </si>
   <si>
     <t xml:space="preserve">FAM65B (RIPOR2)</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000259698.4</t>
+    <t xml:space="preserve">ENST00000259698.8</t>
   </si>
   <si>
     <t xml:space="preserve">2-23</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000538035.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000510784.2</t>
+    <t xml:space="preserve">ENST00000538035.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000510784.8</t>
   </si>
   <si>
     <t xml:space="preserve">-(14,20)</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000540914.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000378023.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ENST00000538035.1</t>
+    <t xml:space="preserve">ENST00000540914.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000378023.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ENST00000538035.6</t>
   </si>
   <si>
     <t xml:space="preserve">RDX</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000343115.4</t>
+    <t xml:space="preserve">ENST00000645495.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000544551.5</t>
   </si>
   <si>
     <t xml:space="preserve">SERPINB6</t>
   </si>
   <si>
+    <t xml:space="preserve">ENST00000380539.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000380529.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000612421.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">ENST00000335686.5</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000380529.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000380546.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000380524.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000380520.1</t>
+    <t xml:space="preserve">transcript_id_retired </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000380524.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000335686.9</t>
   </si>
   <si>
     <t xml:space="preserve">TIMM8A</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000372902.3</t>
+    <t xml:space="preserve">ENST00000372902.4</t>
   </si>
   <si>
     <t xml:space="preserve">TMPRSS3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000433957.2</t>
+    <t xml:space="preserve">ENST00000291532.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000644384.2</t>
   </si>
   <si>
     <t xml:space="preserve">2-13</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000291532.3</t>
+    <t xml:space="preserve">ENST00000474596.5</t>
   </si>
   <si>
     <t xml:space="preserve">ENST00000398397.3</t>
@@ -1342,16 +1363,16 @@
     <t xml:space="preserve">TRIOBP</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000406386.3</t>
+    <t xml:space="preserve">ENST00000644935.1</t>
   </si>
   <si>
     <t xml:space="preserve">3-23</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000403663.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000407319.2</t>
+    <t xml:space="preserve">ENST00000403663.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000407319.7</t>
   </si>
   <si>
     <t xml:space="preserve">-(1,8)</t>
@@ -1360,22 +1381,22 @@
     <t xml:space="preserve">USH1C</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000005226.7</t>
+    <t xml:space="preserve">ENST00000005226.12</t>
   </si>
   <si>
     <t xml:space="preserve">1-18,21-27</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000527020.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000318024.4</t>
+    <t xml:space="preserve">ENST00000527020.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000318024.9</t>
   </si>
   <si>
     <t xml:space="preserve">COL11A1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000358392.2</t>
+    <t xml:space="preserve">ENST00000358392.6</t>
   </si>
   <si>
     <t xml:space="preserve">MHH_HG_diagnostic_panel</t>
@@ -1384,19 +1405,19 @@
     <t xml:space="preserve">COL2A1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000380518.3</t>
+    <t xml:space="preserve">ENST00000380518.8</t>
   </si>
   <si>
     <t xml:space="preserve">COL9A1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000357250.6</t>
+    <t xml:space="preserve">ENST00000357250.11</t>
   </si>
   <si>
     <t xml:space="preserve">COL9A2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000372748.3</t>
+    <t xml:space="preserve">ENST00000372748.8</t>
   </si>
   <si>
     <t xml:space="preserve">FOXI1</t>
@@ -1408,16 +1429,13 @@
     <t xml:space="preserve">KCNJ10</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000368089.3</t>
+    <t xml:space="preserve">ENST00000644903.1</t>
   </si>
   <si>
     <t xml:space="preserve">ROR1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000371079.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ensembl_grch37, longest_prot_coding_trans</t>
+    <t xml:space="preserve">ENST00000371079.6</t>
   </si>
   <si>
     <t xml:space="preserve">PMID: 30894701</t>
@@ -1426,40 +1444,40 @@
     <t xml:space="preserve">EPS8L2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000318562.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ensembl_grch37, longest_prot_coding_trans_with_ncbi_hits</t>
+    <t xml:space="preserve">ENST00000318562.13</t>
   </si>
   <si>
     <t xml:space="preserve">DMXL2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000251076.5</t>
+    <t xml:space="preserve">ENST00000251076.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">longest_prot_coding_trans</t>
   </si>
   <si>
     <t xml:space="preserve">CRYM</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000219599.3</t>
+    <t xml:space="preserve">ENST00000219599.8</t>
   </si>
   <si>
     <t xml:space="preserve">ELMOD3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000315658.7</t>
+    <t xml:space="preserve">ENST00000409013.8</t>
   </si>
   <si>
     <t xml:space="preserve">DIAPH3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000400324.4</t>
+    <t xml:space="preserve">ENST00000400324.9</t>
   </si>
   <si>
     <t xml:space="preserve">DNMT1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000359526.4</t>
+    <t xml:space="preserve">ENST00000359526.9</t>
   </si>
   <si>
     <t xml:space="preserve">lrg_sequence</t>
@@ -1468,82 +1486,88 @@
     <t xml:space="preserve">MCM2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000265056.7</t>
+    <t xml:space="preserve">ENST00000265056.12</t>
   </si>
   <si>
     <t xml:space="preserve">SLC44A4</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000544672.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIAA1199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENST00000394685.3</t>
+    <t xml:space="preserve">ENST00000544672.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEMIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENST00000394685.8</t>
   </si>
   <si>
     <t xml:space="preserve">DSPP</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000399271.1</t>
+    <t xml:space="preserve">ENST00000651931.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">single_transcript</t>
   </si>
   <si>
     <t xml:space="preserve">MYO1F</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000338257.8</t>
+    <t xml:space="preserve">ENST00000644032.2</t>
   </si>
   <si>
     <t xml:space="preserve">TUBB4B</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000340384.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ensembl_grch37, single_prot_coding_trans</t>
+    <t xml:space="preserve">ENST00000340384.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">single_prot_coding_trans</t>
   </si>
   <si>
     <t xml:space="preserve">ABHD12</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000339157.5</t>
+    <t xml:space="preserve">ENST00000339157.10</t>
   </si>
   <si>
     <t xml:space="preserve">NARS2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000281038.5</t>
+    <t xml:space="preserve">ENST00000281038.10</t>
   </si>
   <si>
     <t xml:space="preserve">TNC</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000232975.3</t>
+    <t xml:space="preserve">ENST00000350763.9</t>
   </si>
   <si>
     <t xml:space="preserve">AIFM1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000287295.3</t>
+    <t xml:space="preserve">ENST00000287295.8</t>
   </si>
   <si>
     <t xml:space="preserve">TMEM132E</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000321639.5</t>
+    <t xml:space="preserve">ENST00000631683.2</t>
   </si>
   <si>
     <t xml:space="preserve">GRXCR2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000377976.1</t>
+    <t xml:space="preserve">ENST00000377976.3</t>
   </si>
   <si>
     <t xml:space="preserve">TSPEAR</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000323084.4</t>
+    <t xml:space="preserve">ENST00000323084.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">longest_prot_coding_trans, mane_transcript</t>
   </si>
   <si>
     <t xml:space="preserve">MT-TS1</t>
@@ -1552,13 +1576,13 @@
     <t xml:space="preserve">ENST00000387416.2</t>
   </si>
   <si>
-    <t xml:space="preserve">ensembl_grch37, MT_tRNA</t>
+    <t xml:space="preserve">MT_tRNA</t>
   </si>
   <si>
     <t xml:space="preserve">MYO1A</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000442789.2</t>
+    <t xml:space="preserve">ENST00000442789.6</t>
   </si>
   <si>
     <t xml:space="preserve">MIR96</t>
@@ -1567,61 +1591,64 @@
     <t xml:space="preserve">ENST00000362288.1</t>
   </si>
   <si>
-    <t xml:space="preserve">ensembl_grch37, miRNA</t>
+    <t xml:space="preserve">miRNA</t>
   </si>
   <si>
     <t xml:space="preserve">PNPT1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000447944.2</t>
+    <t xml:space="preserve">ENST00000447944.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mane_transcript, longest_prot_coding_trans</t>
   </si>
   <si>
     <t xml:space="preserve">HOMER2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000304231.8</t>
+    <t xml:space="preserve">ENST00000304231.12</t>
   </si>
   <si>
     <t xml:space="preserve">SLC26A5</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000306312.3</t>
+    <t xml:space="preserve">ENST00000306312.8</t>
   </si>
   <si>
     <t xml:space="preserve">GJA1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000282561.3</t>
+    <t xml:space="preserve">ENST00000282561.4</t>
   </si>
   <si>
     <t xml:space="preserve">MYO1C</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000359786.5</t>
+    <t xml:space="preserve">ENST00000648651.1</t>
   </si>
   <si>
     <t xml:space="preserve">MET</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000318493.6</t>
+    <t xml:space="preserve">ENST00000318493.11</t>
   </si>
   <si>
     <t xml:space="preserve">SLC17A8</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000323346.5</t>
+    <t xml:space="preserve">ENST00000323346.10</t>
   </si>
   <si>
     <t xml:space="preserve">BDP1</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000358731.4</t>
+    <t xml:space="preserve">ENST00000358731.9</t>
   </si>
   <si>
     <t xml:space="preserve">SIX5</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000317578.6</t>
+    <t xml:space="preserve">ENST00000317578.7</t>
   </si>
   <si>
     <t xml:space="preserve">GSDME</t>
@@ -1639,34 +1666,31 @@
     <t xml:space="preserve">DCDC2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000378454.3</t>
+    <t xml:space="preserve">ENST00000378454.8</t>
   </si>
   <si>
     <t xml:space="preserve">TJP2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000377245.4</t>
+    <t xml:space="preserve">ENST00000377245.9</t>
   </si>
   <si>
     <t xml:space="preserve">TMTC2</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000321196.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ensembl_grch37, prot_coding_trans_with_ncbi_hits</t>
+    <t xml:space="preserve">ENST00000321196.8</t>
   </si>
   <si>
     <t xml:space="preserve">GJB3</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000373366.2</t>
+    <t xml:space="preserve">ENST00000373366.3</t>
   </si>
   <si>
     <t xml:space="preserve">COL4A6</t>
   </si>
   <si>
-    <t xml:space="preserve">ENST00000334504.7</t>
+    <t xml:space="preserve">ENST00000334504.12</t>
   </si>
 </sst>
 </file>
@@ -1676,7 +1700,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1698,6 +1722,13 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1707,12 +1738,19 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -1741,12 +1779,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1759,7 +1805,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1780,7 +1826,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E298"/>
-  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="58.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28.48"/>
@@ -1829,19 +1875,22 @@
       <c r="C3" s="0" t="s">
         <v>11</v>
       </c>
+      <c r="D3" s="0" t="s">
+        <v>12</v>
+      </c>
       <c r="E3" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>8</v>
@@ -1849,13 +1898,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>8</v>
@@ -1863,13 +1912,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>8</v>
@@ -1877,13 +1926,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>8</v>
@@ -1891,13 +1940,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>8</v>
@@ -1905,13 +1954,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="0" t="s">
         <v>28</v>
       </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="C9" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>8</v>
@@ -1919,13 +1968,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>8</v>
@@ -1933,13 +1982,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>8</v>
@@ -1947,13 +1996,16 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>40</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>8</v>
@@ -1961,13 +2013,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>8</v>
@@ -1975,13 +2027,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>8</v>
@@ -1989,13 +2041,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>8</v>
@@ -2003,13 +2055,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>8</v>
@@ -2017,13 +2069,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>8</v>
@@ -2031,13 +2083,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>8</v>
@@ -2045,13 +2097,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>8</v>
@@ -2059,13 +2111,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>8</v>
@@ -2073,13 +2125,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E21" s="0" t="s">
         <v>8</v>
@@ -2087,13 +2139,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>8</v>
@@ -2101,13 +2153,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>8</v>
@@ -2115,13 +2167,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>8</v>
@@ -2129,13 +2181,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>8</v>
@@ -2143,28 +2195,28 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="D26" s="2"/>
       <c r="E26" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E27" s="0" t="s">
         <v>8</v>
@@ -2172,13 +2224,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>8</v>
@@ -2186,13 +2238,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>8</v>
@@ -2200,13 +2252,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E30" s="0" t="s">
         <v>8</v>
@@ -2214,13 +2266,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>8</v>
@@ -2228,13 +2280,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>8</v>
@@ -2242,13 +2294,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>8</v>
@@ -2256,13 +2308,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>8</v>
@@ -2270,13 +2322,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>8</v>
@@ -2284,10 +2336,10 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>11</v>
@@ -2298,13 +2350,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>8</v>
@@ -2312,13 +2364,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>8</v>
@@ -2326,13 +2378,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>8</v>
@@ -2340,13 +2392,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E40" s="0" t="s">
         <v>8</v>
@@ -2354,13 +2406,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>8</v>
@@ -2368,13 +2420,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>8</v>
@@ -2382,13 +2434,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E43" s="0" t="s">
         <v>8</v>
@@ -2396,13 +2448,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E44" s="0" t="s">
         <v>8</v>
@@ -2410,13 +2462,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E45" s="0" t="s">
         <v>8</v>
@@ -2424,28 +2476,28 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="D46" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="D46" s="2"/>
       <c r="E46" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E47" s="0" t="s">
         <v>8</v>
@@ -2453,13 +2505,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E48" s="0" t="s">
         <v>8</v>
@@ -2467,13 +2519,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E49" s="0" t="s">
         <v>8</v>
@@ -2481,13 +2533,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E50" s="0" t="s">
         <v>8</v>
@@ -2495,13 +2547,16 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>144</v>
       </c>
       <c r="E51" s="0" t="s">
         <v>8</v>
@@ -2509,13 +2564,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E52" s="0" t="s">
         <v>8</v>
@@ -2523,13 +2578,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E53" s="0" t="s">
         <v>8</v>
@@ -2537,13 +2592,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E54" s="0" t="s">
         <v>8</v>
@@ -2551,13 +2606,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E55" s="0" t="s">
         <v>8</v>
@@ -2565,13 +2620,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E56" s="0" t="s">
         <v>8</v>
@@ -2579,13 +2634,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E57" s="0" t="s">
         <v>8</v>
@@ -2593,13 +2648,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E58" s="0" t="s">
         <v>8</v>
@@ -2607,13 +2662,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E59" s="0" t="s">
         <v>8</v>
@@ -2621,13 +2676,13 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E60" s="0" t="s">
         <v>8</v>
@@ -2635,13 +2690,13 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E61" s="0" t="s">
         <v>8</v>
@@ -2649,13 +2704,13 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E62" s="0" t="s">
         <v>8</v>
@@ -2663,13 +2718,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E63" s="0" t="s">
         <v>8</v>
@@ -2677,13 +2732,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E64" s="0" t="s">
         <v>8</v>
@@ -2691,13 +2746,13 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E65" s="0" t="s">
         <v>8</v>
@@ -2705,13 +2760,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E66" s="0" t="s">
         <v>8</v>
@@ -2719,13 +2774,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E67" s="0" t="s">
         <v>8</v>
@@ -2733,13 +2788,13 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E68" s="0" t="s">
         <v>8</v>
@@ -2747,13 +2802,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E69" s="0" t="s">
         <v>8</v>
@@ -2761,13 +2816,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E70" s="0" t="s">
         <v>8</v>
@@ -2775,27 +2830,27 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E71" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>195</v>
+      <c r="A72" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E72" s="0" t="s">
         <v>8</v>
@@ -2803,527 +2858,527 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>201</v>
+        <v>39</v>
       </c>
       <c r="E73" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
-        <v>202</v>
+      <c r="A74" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C74" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E74" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="B75" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E75" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
-        <v>207</v>
+      <c r="A76" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C76" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E76" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="B77" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E77" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
-        <v>213</v>
+      <c r="A78" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C78" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="E78" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="B79" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E79" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>213</v>
+      <c r="A80" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E80" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
-        <v>220</v>
+      <c r="A81" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C81" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E81" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="B82" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E82" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
-        <v>220</v>
+      <c r="A83" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C83" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="C84" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="E83" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B84" s="0" t="s">
-        <v>227</v>
-      </c>
-      <c r="C84" s="0" t="s">
-        <v>224</v>
-      </c>
       <c r="D84" s="0" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="E84" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
-        <v>220</v>
+      <c r="A85" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="B85" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="C85" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="C87" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="C88" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E88" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="C89" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="C85" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D85" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="E85" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B86" s="0" t="s">
-        <v>229</v>
-      </c>
-      <c r="C86" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D86" s="0" t="s">
-        <v>230</v>
-      </c>
-      <c r="E86" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B87" s="0" t="s">
-        <v>232</v>
-      </c>
-      <c r="C87" s="0" t="s">
+      <c r="E89" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E87" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B88" s="0" t="s">
+      <c r="B90" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="C90" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B92" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="C88" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="E88" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B89" s="0" t="s">
+      <c r="C92" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E92" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B93" s="0" t="s">
         <v>236</v>
       </c>
-      <c r="C89" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="E89" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B90" s="0" t="s">
+      <c r="C93" s="0" t="s">
         <v>237</v>
       </c>
-      <c r="C90" s="0" t="s">
-        <v>238</v>
-      </c>
-      <c r="E90" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B91" s="0" t="s">
+      <c r="D93" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="E94" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B95" s="0" t="s">
         <v>239</v>
       </c>
-      <c r="C91" s="0" t="s">
-        <v>240</v>
-      </c>
-      <c r="E91" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B92" s="0" t="s">
-        <v>232</v>
-      </c>
-      <c r="C92" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="E92" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B93" s="0" t="s">
-        <v>234</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="D93" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="E93" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B94" s="0" t="s">
-        <v>234</v>
-      </c>
-      <c r="C94" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D94" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="E94" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B95" s="0" t="s">
+      <c r="C95" s="0" t="s">
         <v>237</v>
       </c>
-      <c r="C95" s="0" t="s">
-        <v>235</v>
-      </c>
       <c r="E95" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
-        <v>243</v>
+      <c r="A96" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="B96" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="E97" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="C99" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E99" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="D100" s="0" t="s">
         <v>244</v>
       </c>
-      <c r="C96" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E96" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B97" s="0" t="s">
+      <c r="E100" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C97" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E97" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B98" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="C98" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E98" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B99" s="0" t="s">
-        <v>247</v>
-      </c>
-      <c r="C99" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E99" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B100" s="0" t="s">
+      <c r="B101" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="C101" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E101" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E104" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="D105" s="0" t="s">
         <v>244</v>
       </c>
-      <c r="C100" s="0" t="s">
-        <v>248</v>
-      </c>
-      <c r="D100" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="E100" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B101" s="0" t="s">
-        <v>249</v>
-      </c>
-      <c r="C101" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="E101" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B102" s="0" t="s">
+      <c r="E105" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="C107" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E107" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="C108" s="0" t="s">
         <v>251</v>
-      </c>
-      <c r="C102" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E102" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B103" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="C103" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E103" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B104" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="C104" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E104" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B105" s="0" t="s">
-        <v>251</v>
-      </c>
-      <c r="C105" s="0" t="s">
-        <v>254</v>
-      </c>
-      <c r="D105" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="E105" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B106" s="0" t="s">
-        <v>256</v>
-      </c>
-      <c r="C106" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E106" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B107" s="0" t="s">
-        <v>257</v>
-      </c>
-      <c r="C107" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="E107" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B108" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="C108" s="0" t="s">
-        <v>248</v>
       </c>
       <c r="E108" s="0" t="s">
         <v>8</v>
@@ -3331,10 +3386,10 @@
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C109" s="0" t="n">
         <v>3</v>
@@ -3344,377 +3399,380 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
-        <v>261</v>
+      <c r="A110" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E110" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
-        <v>261</v>
+      <c r="A111" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C111" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E111" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="B112" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E112" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
-        <v>261</v>
+      <c r="A113" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E113" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
-        <v>268</v>
+      <c r="A114" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E114" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
-        <v>268</v>
+      <c r="A115" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E115" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
-        <v>268</v>
+      <c r="A116" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="B116" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="C116" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E116" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C116" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E116" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="B117" s="0" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E117" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="s">
-        <v>272</v>
+      <c r="A118" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E118" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
-        <v>272</v>
+      <c r="A119" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E119" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
-        <v>272</v>
+      <c r="A120" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="E120" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="s">
-        <v>278</v>
+      <c r="A121" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>201</v>
+        <v>39</v>
       </c>
       <c r="E121" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
-        <v>278</v>
+      <c r="A122" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E122" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1" t="s">
-        <v>278</v>
+      <c r="A123" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E123" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="s">
-        <v>278</v>
+      <c r="A124" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>282</v>
+        <v>285</v>
+      </c>
+      <c r="D124" s="0" t="s">
+        <v>244</v>
       </c>
       <c r="E124" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="s">
-        <v>283</v>
+      <c r="A125" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E125" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1" t="s">
-        <v>283</v>
+      <c r="A126" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E126" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1" t="s">
-        <v>283</v>
+      <c r="A127" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E127" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="s">
-        <v>283</v>
+      <c r="A128" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="B128" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="C128" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E128" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C128" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="E128" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="B129" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E129" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1" t="s">
-        <v>283</v>
+      <c r="A130" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E130" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1" t="s">
-        <v>289</v>
+      <c r="A131" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C131" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="E131" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="E131" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="B132" s="0" t="s">
         <v>292</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E132" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="1" t="s">
-        <v>289</v>
+      <c r="A133" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E133" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="s">
-        <v>289</v>
+      <c r="A134" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="B134" s="0" t="s">
         <v>295</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E134" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="1" t="s">
-        <v>289</v>
+      <c r="A135" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="B135" s="0" t="s">
         <v>296</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E135" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="1" t="s">
+      <c r="A136" s="2" t="s">
         <v>297</v>
       </c>
       <c r="B136" s="0" t="s">
@@ -3728,49 +3786,49 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="1" t="s">
+      <c r="A137" s="2" t="s">
         <v>297</v>
       </c>
       <c r="B137" s="0" t="s">
         <v>300</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E137" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1" t="s">
+      <c r="A138" s="2" t="s">
         <v>297</v>
       </c>
       <c r="B138" s="0" t="s">
         <v>301</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E138" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="1" t="s">
+      <c r="A139" s="2" t="s">
         <v>297</v>
       </c>
       <c r="B139" s="0" t="s">
         <v>300</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E139" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1" t="s">
+      <c r="A140" s="2" t="s">
         <v>297</v>
       </c>
       <c r="B140" s="0" t="s">
@@ -3784,7 +3842,7 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1" t="s">
+      <c r="A141" s="2" t="s">
         <v>304</v>
       </c>
       <c r="B141" s="0" t="s">
@@ -3793,102 +3851,105 @@
       <c r="C141" s="0" t="s">
         <v>306</v>
       </c>
+      <c r="D141" s="0" t="s">
+        <v>248</v>
+      </c>
       <c r="E141" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="1" t="s">
+      <c r="A142" s="2" t="s">
         <v>304</v>
       </c>
       <c r="B142" s="0" t="s">
         <v>307</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E142" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="1" t="s">
+      <c r="A143" s="2" t="s">
         <v>304</v>
       </c>
       <c r="B143" s="0" t="s">
         <v>308</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E143" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1" t="s">
+      <c r="A144" s="2" t="s">
         <v>304</v>
       </c>
       <c r="B144" s="0" t="s">
         <v>308</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E144" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="1" t="s">
+      <c r="A145" s="2" t="s">
         <v>304</v>
       </c>
       <c r="B145" s="0" t="s">
         <v>309</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E145" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
+      <c r="A146" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B146" s="0" t="s">
         <v>311</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E146" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="1" t="s">
+      <c r="A147" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B147" s="0" t="s">
         <v>311</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E147" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1" t="s">
+      <c r="A148" s="2" t="s">
         <v>312</v>
       </c>
       <c r="B148" s="0" t="s">
@@ -3902,21 +3963,21 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="1" t="s">
+      <c r="A149" s="2" t="s">
         <v>312</v>
       </c>
       <c r="B149" s="0" t="s">
         <v>315</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E149" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1" t="s">
+      <c r="A150" s="2" t="s">
         <v>312</v>
       </c>
       <c r="B150" s="0" t="s">
@@ -3930,21 +3991,21 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="1" t="s">
+      <c r="A151" s="2" t="s">
         <v>312</v>
       </c>
       <c r="B151" s="0" t="s">
         <v>318</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E151" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="1" t="s">
+      <c r="A152" s="2" t="s">
         <v>312</v>
       </c>
       <c r="B152" s="0" t="s">
@@ -3958,52 +4019,52 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
+      <c r="A153" s="2" t="s">
         <v>321</v>
       </c>
       <c r="B153" s="0" t="s">
         <v>322</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E153" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="s">
+      <c r="A154" s="2" t="s">
         <v>321</v>
       </c>
       <c r="B154" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="C154" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E154" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B155" s="0" t="s">
         <v>323</v>
       </c>
-      <c r="C154" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E154" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B155" s="0" t="s">
+      <c r="C155" s="0" t="s">
         <v>324</v>
       </c>
-      <c r="C155" s="0" t="s">
+      <c r="E155" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="E155" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B156" s="0" t="s">
+      <c r="B156" s="1" t="s">
         <v>326</v>
       </c>
       <c r="C156" s="0" t="s">
@@ -4014,66 +4075,69 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="1" t="s">
-        <v>321</v>
+      <c r="A157" s="2" t="s">
+        <v>325</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
+      </c>
+      <c r="D157" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="E157" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="s">
-        <v>321</v>
+      <c r="A158" s="2" t="s">
+        <v>325</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E158" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="1" t="s">
-        <v>321</v>
+      <c r="A159" s="2" t="s">
+        <v>325</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E159" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1" t="s">
-        <v>321</v>
+      <c r="A160" s="2" t="s">
+        <v>325</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E160" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1" t="s">
+      <c r="A161" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B161" s="0" t="s">
@@ -4087,35 +4151,38 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="1" t="s">
+      <c r="A162" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B162" s="0" t="s">
         <v>333</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
+      </c>
+      <c r="D162" s="0" t="s">
+        <v>144</v>
       </c>
       <c r="E162" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="1" t="s">
+      <c r="A163" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B163" s="0" t="s">
         <v>334</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E163" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1" t="s">
+      <c r="A164" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B164" s="0" t="s">
@@ -4129,94 +4196,94 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1" t="s">
+      <c r="A165" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B165" s="0" t="s">
         <v>337</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E165" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="1" t="s">
+      <c r="A166" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D166" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E166" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="1" t="s">
+      <c r="A167" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E167" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="1" t="s">
+      <c r="A168" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B168" s="0" t="s">
         <v>339</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E168" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="1" t="s">
+      <c r="A169" s="2" t="s">
         <v>340</v>
       </c>
       <c r="B169" s="0" t="s">
         <v>341</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E169" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="1" t="s">
+      <c r="A170" s="2" t="s">
         <v>340</v>
       </c>
       <c r="B170" s="0" t="s">
         <v>342</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E170" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="1" t="s">
+      <c r="A171" s="2" t="s">
         <v>340</v>
       </c>
       <c r="B171" s="0" t="s">
@@ -4230,21 +4297,21 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="1" t="s">
+      <c r="A172" s="2" t="s">
         <v>340</v>
       </c>
       <c r="B172" s="0" t="s">
         <v>344</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E172" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="1" t="s">
+      <c r="A173" s="2" t="s">
         <v>345</v>
       </c>
       <c r="B173" s="0" t="s">
@@ -4258,7 +4325,7 @@
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="1" t="s">
+      <c r="A174" s="2" t="s">
         <v>345</v>
       </c>
       <c r="B174" s="0" t="s">
@@ -4272,21 +4339,21 @@
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="1" t="s">
+      <c r="A175" s="2" t="s">
         <v>345</v>
       </c>
       <c r="B175" s="0" t="s">
         <v>350</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E175" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="1" t="s">
+      <c r="A176" s="2" t="s">
         <v>351</v>
       </c>
       <c r="B176" s="0" t="s">
@@ -4300,21 +4367,21 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="1" t="s">
+      <c r="A177" s="2" t="s">
         <v>351</v>
       </c>
       <c r="B177" s="0" t="s">
         <v>353</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E177" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="1" t="s">
+      <c r="A178" s="2" t="s">
         <v>351</v>
       </c>
       <c r="B178" s="0" t="s">
@@ -4328,49 +4395,49 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="1" t="s">
+      <c r="A179" s="2" t="s">
         <v>356</v>
       </c>
       <c r="B179" s="0" t="s">
         <v>357</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E179" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="1" t="s">
+      <c r="A180" s="2" t="s">
         <v>356</v>
       </c>
       <c r="B180" s="0" t="s">
         <v>358</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E180" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="1" t="s">
+      <c r="A181" s="2" t="s">
         <v>356</v>
       </c>
       <c r="B181" s="0" t="s">
         <v>359</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E181" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="1" t="s">
+      <c r="A182" s="2" t="s">
         <v>360</v>
       </c>
       <c r="B182" s="0" t="s">
@@ -4384,7 +4451,7 @@
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="1" t="s">
+      <c r="A183" s="2" t="s">
         <v>360</v>
       </c>
       <c r="B183" s="0" t="s">
@@ -4398,7 +4465,7 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="1" t="s">
+      <c r="A184" s="2" t="s">
         <v>360</v>
       </c>
       <c r="B184" s="0" t="s">
@@ -4412,21 +4479,21 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="1" t="s">
+      <c r="A185" s="2" t="s">
         <v>360</v>
       </c>
       <c r="B185" s="0" t="s">
         <v>367</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E185" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="1" t="s">
+      <c r="A186" s="2" t="s">
         <v>360</v>
       </c>
       <c r="B186" s="0" t="s">
@@ -4440,7 +4507,7 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="1" t="s">
+      <c r="A187" s="2" t="s">
         <v>369</v>
       </c>
       <c r="B187" s="0" t="s">
@@ -4454,7 +4521,7 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="1" t="s">
+      <c r="A188" s="2" t="s">
         <v>369</v>
       </c>
       <c r="B188" s="0" t="s">
@@ -4468,10 +4535,10 @@
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="1" t="s">
+      <c r="A189" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B189" s="0" t="s">
+      <c r="B189" s="2" t="s">
         <v>375</v>
       </c>
       <c r="C189" s="0" t="s">
@@ -4482,25 +4549,25 @@
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="1" t="s">
+      <c r="A190" s="2" t="s">
         <v>374</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E190" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="1" t="s">
+      <c r="A191" s="2" t="s">
         <v>374</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C191" s="0" t="s">
         <v>332</v>
@@ -4510,67 +4577,67 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="1" t="s">
+      <c r="A192" s="2" t="s">
         <v>374</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E192" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="1" t="s">
+      <c r="A193" s="2" t="s">
         <v>374</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C193" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E193" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B194" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="C194" s="0" t="s">
         <v>219</v>
       </c>
-      <c r="E193" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="1" t="s">
+      <c r="E194" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B194" s="0" t="s">
-        <v>379</v>
-      </c>
-      <c r="C194" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="E194" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="s">
+      <c r="B195" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="C195" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="E195" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B195" s="0" t="s">
-        <v>380</v>
-      </c>
-      <c r="C195" s="0" t="s">
-        <v>381</v>
-      </c>
-      <c r="E195" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="B196" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C196" s="0" t="s">
         <v>303</v>
@@ -4580,441 +4647,435 @@
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="1" t="s">
-        <v>383</v>
+      <c r="A197" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="B197" s="0" t="s">
+        <v>385</v>
+      </c>
+      <c r="C197" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="E197" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C197" s="0" t="s">
-        <v>385</v>
-      </c>
-      <c r="E197" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="B198" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="C198" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E198" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C198" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E198" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="B199" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D199" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E199" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="1" t="s">
-        <v>383</v>
+      <c r="A200" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="B200" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="C200" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E200" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C200" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E200" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="B201" s="0" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E201" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="1" t="s">
-        <v>383</v>
+      <c r="A202" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="B202" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="C202" s="0" t="s">
+        <v>393</v>
+      </c>
+      <c r="E202" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B203" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="C203" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E203" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B204" s="0" t="s">
+        <v>395</v>
+      </c>
+      <c r="C204" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E204" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B205" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="C205" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E205" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B206" s="0" t="s">
         <v>389</v>
       </c>
-      <c r="C202" s="0" t="s">
-        <v>390</v>
-      </c>
-      <c r="E202" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="B203" s="0" t="s">
-        <v>389</v>
-      </c>
-      <c r="C203" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E203" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="B204" s="0" t="s">
-        <v>391</v>
-      </c>
-      <c r="C204" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E204" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="B205" s="0" t="s">
-        <v>392</v>
-      </c>
-      <c r="C205" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E205" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="B206" s="0" t="s">
+      <c r="C206" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="D206" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="E206" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C206" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E206" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="B207" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E207" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="1" t="s">
-        <v>383</v>
+      <c r="A208" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D208" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E208" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="1" t="s">
-        <v>383</v>
+      <c r="A209" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D209" s="0" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E209" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="1" t="s">
-        <v>383</v>
+      <c r="A210" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="B210" s="0" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E210" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="1" t="s">
-        <v>383</v>
+      <c r="A211" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="B211" s="0" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D211" s="0" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E211" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="1" t="s">
-        <v>383</v>
+      <c r="A212" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="B212" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E212" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="1" t="s">
-        <v>383</v>
+      <c r="A213" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="B213" s="0" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E213" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="1" t="s">
-        <v>400</v>
+      <c r="A214" s="2" t="s">
+        <v>403</v>
       </c>
       <c r="B214" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>402</v>
-      </c>
-      <c r="D214" s="0" t="s">
-        <v>230</v>
+        <v>405</v>
       </c>
       <c r="E214" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="1" t="s">
-        <v>400</v>
+      <c r="A215" s="2" t="s">
+        <v>403</v>
       </c>
       <c r="B215" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="C215" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="E215" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C215" s="0" t="s">
-        <v>404</v>
-      </c>
-      <c r="E215" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="B216" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D216" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E216" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="1" t="s">
-        <v>406</v>
+      <c r="A217" s="2" t="s">
+        <v>409</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C217" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="E217" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B218" s="0" t="s">
+        <v>410</v>
+      </c>
+      <c r="C218" s="0" t="s">
         <v>408</v>
       </c>
-      <c r="E217" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B218" s="0" t="s">
-        <v>407</v>
-      </c>
-      <c r="C218" s="0" t="s">
-        <v>405</v>
-      </c>
       <c r="D218" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E218" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="1" t="s">
-        <v>406</v>
+      <c r="A219" s="2" t="s">
+        <v>409</v>
       </c>
       <c r="B219" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="C219" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="E219" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C219" s="0" t="s">
+      <c r="B220" s="0" t="s">
         <v>410</v>
       </c>
-      <c r="E219" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B220" s="0" t="s">
-        <v>411</v>
-      </c>
       <c r="C220" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E220" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="1" t="s">
-        <v>406</v>
+      <c r="A221" s="2" t="s">
+        <v>409</v>
       </c>
       <c r="B221" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E221" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="1" t="s">
-        <v>406</v>
+      <c r="A222" s="2" t="s">
+        <v>409</v>
       </c>
       <c r="B222" s="0" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E222" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="1" t="s">
-        <v>406</v>
+      <c r="A223" s="2" t="s">
+        <v>409</v>
       </c>
       <c r="B223" s="0" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E223" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="1" t="s">
-        <v>406</v>
+      <c r="A224" s="2" t="s">
+        <v>409</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E224" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="1" t="s">
-        <v>415</v>
+      <c r="A225" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E225" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="1" t="s">
-        <v>415</v>
+      <c r="A226" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>336</v>
@@ -5024,39 +5085,39 @@
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="1" t="s">
-        <v>415</v>
+      <c r="A227" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E227" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="1" t="s">
-        <v>415</v>
+      <c r="A228" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E228" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="1" t="s">
-        <v>415</v>
+      <c r="A229" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C229" s="0" t="n">
         <v>-14</v>
@@ -5066,101 +5127,101 @@
       </c>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="1" t="s">
-        <v>415</v>
+      <c r="A230" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D230" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E230" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="1" t="s">
-        <v>415</v>
+      <c r="A231" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="B231" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D231" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E231" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="1" t="s">
-        <v>424</v>
+      <c r="A232" s="2" t="s">
+        <v>427</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E232" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="1" t="s">
-        <v>424</v>
+      <c r="A233" s="2" t="s">
+        <v>427</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C233" s="0" t="s">
         <v>320</v>
       </c>
       <c r="D233" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E233" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="1" t="s">
-        <v>426</v>
+      <c r="A234" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E234" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="1" t="s">
-        <v>426</v>
+      <c r="A235" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="B235" s="0" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D235" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E235" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="1" t="s">
-        <v>426</v>
+      <c r="A236" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="B236" s="0" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C236" s="0" t="s">
         <v>336</v>
@@ -5170,163 +5231,166 @@
       </c>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="1" t="s">
-        <v>426</v>
+      <c r="A237" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="B237" s="0" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E237" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="1" t="s">
-        <v>426</v>
+      <c r="A238" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="B238" s="0" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D238" s="0" t="s">
-        <v>242</v>
+        <v>221</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>435</v>
       </c>
       <c r="E238" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="1" t="s">
-        <v>426</v>
+      <c r="A239" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="B239" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C239" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="E239" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C239" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="E239" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="B240" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C240" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="D240" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="E240" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C240" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D240" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="E240" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="B241" s="0" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
+      </c>
+      <c r="D241" s="0" t="s">
+        <v>144</v>
       </c>
       <c r="E241" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="1" t="s">
-        <v>432</v>
+      <c r="A242" s="2" t="s">
+        <v>438</v>
       </c>
       <c r="B242" s="0" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E242" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="1" t="s">
-        <v>432</v>
+      <c r="A243" s="2" t="s">
+        <v>438</v>
       </c>
       <c r="B243" s="0" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C243" s="0" t="s">
         <v>373</v>
       </c>
       <c r="D243" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E243" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="1" t="s">
-        <v>434</v>
+      <c r="A244" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="B244" s="0" t="s">
-        <v>435</v>
-      </c>
-      <c r="C244" s="0" t="s">
-        <v>436</v>
+        <v>441</v>
+      </c>
+      <c r="D244" s="0" t="s">
+        <v>144</v>
       </c>
       <c r="E244" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="1" t="s">
-        <v>434</v>
+      <c r="A245" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="B245" s="0" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>219</v>
+        <v>443</v>
       </c>
       <c r="D245" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E245" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="1" t="s">
-        <v>434</v>
+      <c r="A246" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="B246" s="0" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E246" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="1" t="s">
-        <v>434</v>
+      <c r="A247" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="B247" s="0" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="C247" s="0" t="s">
         <v>376</v>
@@ -5336,840 +5400,843 @@
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="1" t="s">
-        <v>439</v>
+      <c r="A248" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="B248" s="0" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="E248" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="1" t="s">
-        <v>439</v>
+      <c r="A249" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="B249" s="0" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E249" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="1" t="s">
-        <v>439</v>
+      <c r="A250" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="B250" s="0" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="E250" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="1" t="s">
-        <v>445</v>
+      <c r="A251" s="2" t="s">
+        <v>452</v>
       </c>
       <c r="B251" s="0" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E251" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="1" t="s">
-        <v>445</v>
+      <c r="A252" s="2" t="s">
+        <v>452</v>
       </c>
       <c r="B252" s="0" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E252" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="1" t="s">
-        <v>445</v>
+      <c r="A253" s="2" t="s">
+        <v>452</v>
       </c>
       <c r="B253" s="0" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E253" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>451</v>
+      <c r="A254" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>458</v>
       </c>
       <c r="C254" s="0" t="s">
         <v>366</v>
       </c>
       <c r="E254" s="0" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>454</v>
+      <c r="A255" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>461</v>
       </c>
       <c r="C255" s="0" t="s">
         <v>366</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="B256" s="3" t="s">
-        <v>456</v>
+      <c r="A256" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>463</v>
       </c>
       <c r="C256" s="0" t="s">
         <v>366</v>
       </c>
       <c r="E256" s="0" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>458</v>
+      <c r="A257" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>465</v>
       </c>
       <c r="C257" s="0" t="s">
         <v>366</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>460</v>
+      <c r="A258" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>467</v>
       </c>
       <c r="C258" s="0" t="s">
         <v>366</v>
       </c>
       <c r="E258" s="0" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="B259" s="3" t="s">
-        <v>462</v>
+      <c r="A259" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>469</v>
       </c>
       <c r="C259" s="0" t="s">
         <v>366</v>
       </c>
+      <c r="D259" s="0" t="s">
+        <v>12</v>
+      </c>
       <c r="E259" s="0" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="0" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="B260" s="0" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="C260" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="E260" s="4" t="s">
-        <v>466</v>
+        <v>12</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="4" t="s">
-        <v>467</v>
+      <c r="A261" s="1" t="s">
+        <v>473</v>
       </c>
       <c r="B261" s="0" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C261" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>469</v>
-      </c>
-      <c r="E261" s="4" t="s">
-        <v>466</v>
+        <v>12</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="0" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B262" s="0" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C262" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="0" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B263" s="0" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C263" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="0" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B264" s="0" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C264" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D264" s="0" t="s">
-        <v>465</v>
+        <v>12</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="0" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B265" s="0" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C265" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="E265" s="4" t="s">
-        <v>466</v>
+        <v>477</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="4" t="s">
-        <v>478</v>
+      <c r="A266" s="1" t="s">
+        <v>484</v>
       </c>
       <c r="B266" s="0" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C266" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>480</v>
-      </c>
-      <c r="E266" s="4" t="s">
-        <v>466</v>
+        <v>486</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="4" t="s">
-        <v>481</v>
+      <c r="A267" s="1" t="s">
+        <v>487</v>
       </c>
       <c r="B267" s="0" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C267" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="E267" s="4" t="s">
-        <v>466</v>
+        <v>477</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="4" t="s">
-        <v>483</v>
+      <c r="A268" s="1" t="s">
+        <v>489</v>
       </c>
       <c r="B268" s="0" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C268" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="E268" s="4" t="s">
-        <v>466</v>
+        <v>477</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="B269" s="0" t="s">
-        <v>486</v>
+      <c r="A269" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>492</v>
       </c>
       <c r="C269" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="E269" s="4" t="s">
-        <v>466</v>
+        <v>477</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="0" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B270" s="0" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C270" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D270" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="E270" s="4" t="s">
-        <v>466</v>
+        <v>495</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="0" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B271" s="0" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="C271" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="E271" s="4" t="s">
-        <v>466</v>
+        <v>12</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="0" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B272" s="0" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C272" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="0" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B273" s="0" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="C273" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D273" s="0" t="s">
-        <v>465</v>
+        <v>12</v>
       </c>
       <c r="E273" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="4" t="s">
-        <v>496</v>
+      <c r="A274" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="B274" s="0" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C274" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>465</v>
+        <v>12</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="0" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B275" s="0" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="C275" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D275" s="0" t="s">
-        <v>480</v>
+        <v>12</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="4" t="s">
-        <v>500</v>
+      <c r="A276" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="B276" s="0" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C276" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="0" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B277" s="0" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C277" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D277" s="0" t="s">
-        <v>493</v>
+        <v>12</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="0" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B278" s="0" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C278" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>493</v>
+        <v>12</v>
       </c>
       <c r="E278" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="0" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B279" s="0" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C279" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D279" s="0" t="s">
-        <v>465</v>
+        <v>515</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="0" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B280" s="0" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C280" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="E280" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="0" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B281" s="0" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="C281" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="0" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B282" s="0" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C282" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D282" s="0" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="0" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B283" s="0" t="s">
-        <v>517</v>
-      </c>
-      <c r="C283" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C283" s="2" t="s">
         <v>366</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>465</v>
+        <v>526</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="0" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B284" s="0" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="C284" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D284" s="0" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="4" t="s">
-        <v>520</v>
+      <c r="A285" s="1" t="s">
+        <v>529</v>
       </c>
       <c r="B285" s="0" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="C285" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>465</v>
+        <v>12</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="0" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="B286" s="0" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="C286" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>480</v>
+        <v>12</v>
       </c>
       <c r="E286" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="0" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="B287" s="0" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C287" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>465</v>
+        <v>12</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="0" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="B288" s="0" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="C288" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D288" s="0" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="E288" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="0" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B289" s="0" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="C289" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="0" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="B290" s="0" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="C290" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E290" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="0" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="B291" s="0" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="C291" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D291" s="0" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="0" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="B292" s="0" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="C292" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D292" s="0" t="s">
-        <v>230</v>
+        <v>12</v>
       </c>
       <c r="E292" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="0" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="B293" s="0" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="C293" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="0" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B294" s="0" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C294" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="0" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="B295" s="0" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="C295" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="0" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="B296" s="0" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C296" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>544</v>
+        <v>12</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="0" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B297" s="0" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="C297" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D297" s="0" t="s">
-        <v>465</v>
+        <v>12</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="0" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B298" s="0" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="C298" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>480</v>
+        <v>12</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
